--- a/dados/COPA_REVOADA_planilha.xlsx
+++ b/dados/COPA_REVOADA_planilha.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="15" min="1" max="2"/>
@@ -1732,58 +1732,70 @@
     <row r="8" ht="15" customHeight="1" s="16">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>bernardoc</t>
+          <t>borba</t>
         </is>
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>Bernardo C</t>
+          <t>Borba</t>
         </is>
       </c>
       <c r="C8" s="26" t="n"/>
       <c r="D8" s="26" t="n"/>
       <c r="E8" s="26" t="n"/>
-      <c r="F8" s="25" t="n"/>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>Bernardo C</t>
+          <t>Borba / borba</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="16">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>bernardom</t>
+          <t>bruno</t>
         </is>
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>Bernardo M</t>
+          <t>Bruno</t>
         </is>
       </c>
       <c r="C9" s="26" t="n"/>
       <c r="D9" s="26" t="n"/>
       <c r="E9" s="26" t="n"/>
-      <c r="F9" s="25" t="n"/>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>Bernardo M</t>
+          <t>Bruno / bruno</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="16">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>borba</t>
+          <t>correa</t>
         </is>
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>Borba</t>
+          <t>Be Correa</t>
         </is>
       </c>
       <c r="C10" s="26" t="n"/>
-      <c r="D10" s="26" t="n"/>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>GOL</t>
+        </is>
+      </c>
       <c r="E10" s="26" t="n"/>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -1792,19 +1804,19 @@
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>Borba / borba</t>
+          <t>Correa / bernardoc</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="16">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>bruno</t>
+          <t>danilim</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>Bruno</t>
+          <t>Danilim</t>
         </is>
       </c>
       <c r="C11" s="26" t="n"/>
@@ -1817,19 +1829,19 @@
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>Bruno / bruno</t>
+          <t>Danilim / danilim</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="16">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>correa</t>
+          <t>davi</t>
         </is>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Correa</t>
+          <t>Davi</t>
         </is>
       </c>
       <c r="C12" s="26" t="n"/>
@@ -1842,69 +1854,61 @@
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>Correa</t>
+          <t>davi</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="16">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>danilim</t>
+          <t>dereck</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Danilim</t>
+          <t>Dereck</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
       <c r="D13" s="26" t="n"/>
       <c r="E13" s="26" t="n"/>
-      <c r="F13" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="F13" s="25" t="n"/>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>Danilim / danilim</t>
+          <t>Dereck</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="16">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>davi</t>
+          <t>derek</t>
         </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>Davi</t>
+          <t>Derek</t>
         </is>
       </c>
       <c r="C14" s="26" t="n"/>
       <c r="D14" s="26" t="n"/>
       <c r="E14" s="26" t="n"/>
-      <c r="F14" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="F14" s="25" t="n"/>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>davi</t>
+          <t>Derek / derek</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="16">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>dereck</t>
+          <t>dereka</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>Dereck</t>
+          <t>Dereka</t>
         </is>
       </c>
       <c r="C15" s="26" t="n"/>
@@ -1913,61 +1917,69 @@
       <c r="F15" s="25" t="n"/>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>Dereck</t>
+          <t>Dereka</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="16">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>derek</t>
+          <t>enzo</t>
         </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>Derek</t>
+          <t>Enzo</t>
         </is>
       </c>
       <c r="C16" s="26" t="n"/>
       <c r="D16" s="26" t="n"/>
       <c r="E16" s="26" t="n"/>
-      <c r="F16" s="25" t="n"/>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>Derek / derek</t>
+          <t>Enzo / enzo</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="16">
       <c r="A17" s="25" t="inlineStr">
         <is>
-          <t>dereka</t>
+          <t>fanta</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>Dereka</t>
+          <t>Fanta</t>
         </is>
       </c>
       <c r="C17" s="26" t="n"/>
       <c r="D17" s="26" t="n"/>
       <c r="E17" s="26" t="n"/>
-      <c r="F17" s="25" t="n"/>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>Dereka</t>
+          <t>Fanta / fanta</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="16">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>enzo</t>
+          <t>garopaba</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>Enzo</t>
+          <t>Garopaba</t>
         </is>
       </c>
       <c r="C18" s="26" t="n"/>
@@ -1980,19 +1992,19 @@
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>Enzo / enzo</t>
+          <t>Garopa / Garopaba / garopa / garopaba</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="16">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>fanta</t>
+          <t>glauber</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>Fanta</t>
+          <t>Glauber</t>
         </is>
       </c>
       <c r="C19" s="26" t="n"/>
@@ -2005,19 +2017,19 @@
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>Fanta / fanta</t>
+          <t>Glauber / glauber</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="16">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>garopaba</t>
+          <t>hanon</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Garopaba</t>
+          <t>Hanon</t>
         </is>
       </c>
       <c r="C20" s="26" t="n"/>
@@ -2030,19 +2042,19 @@
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>Garopa / Garopaba / garopa / garopaba</t>
+          <t>Hanon / hanon</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="16">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>glauber</t>
+          <t>henrique</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>Glauber</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="C21" s="26" t="n"/>
@@ -2055,40 +2067,44 @@
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>Glauber / glauber</t>
+          <t>Henrique</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="16">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>gordo</t>
+          <t>joao</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>Gordo</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C22" s="26" t="n"/>
       <c r="D22" s="26" t="n"/>
       <c r="E22" s="26" t="n"/>
-      <c r="F22" s="25" t="n"/>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>Gordo</t>
+          <t>Joao</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="16">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>hanon</t>
+          <t>kretzer</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>Hanon</t>
+          <t>Kretzer</t>
         </is>
       </c>
       <c r="C23" s="26" t="n"/>
@@ -2101,19 +2117,19 @@
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>Hanon / hanon</t>
+          <t>Kretzer / kretzer / vitim</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="16">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>henrique</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="C24" s="26" t="n"/>
@@ -2126,19 +2142,19 @@
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>Leo / leo</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="16">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>joao</t>
+          <t>leobittencourt</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Leobittencourt</t>
         </is>
       </c>
       <c r="C25" s="26" t="n"/>
@@ -2149,21 +2165,17 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="G25" s="25" t="inlineStr">
-        <is>
-          <t>Joao</t>
-        </is>
-      </c>
+      <c r="G25" s="25" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="16">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>kretzer</t>
+          <t>leogodinho</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>Kretzer</t>
+          <t>Leo Godinho</t>
         </is>
       </c>
       <c r="C26" s="26" t="n"/>
@@ -2176,19 +2188,19 @@
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>Kretzer / kretzer</t>
+          <t>Leo Godinho</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="16">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>letti</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Letti</t>
         </is>
       </c>
       <c r="C27" s="26" t="n"/>
@@ -2201,19 +2213,19 @@
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>Leo / leo</t>
+          <t>Letti / letti</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="16">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>leobittencourt</t>
+          <t>luigi</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>Leobittencourt</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C28" s="26" t="n"/>
@@ -2224,17 +2236,21 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="G28" s="25" t="n"/>
+      <c r="G28" s="25" t="inlineStr">
+        <is>
+          <t>Luigi</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="16">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>leogodinho</t>
+          <t>marucco</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>Leo Godinho</t>
+          <t>Be Marucco</t>
         </is>
       </c>
       <c r="C29" s="26" t="n"/>
@@ -2247,19 +2263,19 @@
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>Leo Godinho</t>
+          <t>Marucco / bernardom</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="16">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>letti</t>
+          <t>matheus</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>Letti</t>
+          <t>Matheus</t>
         </is>
       </c>
       <c r="C30" s="26" t="n"/>
@@ -2272,23 +2288,27 @@
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>Letti / letti</t>
+          <t>matheus</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="16">
       <c r="A31" s="25" t="inlineStr">
         <is>
-          <t>luigi</t>
+          <t>merizi</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>Luigi</t>
+          <t>Merizi GK</t>
         </is>
       </c>
       <c r="C31" s="26" t="n"/>
-      <c r="D31" s="26" t="n"/>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>GOL</t>
+        </is>
+      </c>
       <c r="E31" s="26" t="n"/>
       <c r="F31" s="25" t="inlineStr">
         <is>
@@ -2297,19 +2317,19 @@
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>Luigi</t>
+          <t>Merizi / Merizi GK / merizi</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="16">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>marucco</t>
+          <t>miniderek</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>Marucco</t>
+          <t>Mini Derek</t>
         </is>
       </c>
       <c r="C32" s="26" t="n"/>
@@ -2322,52 +2342,44 @@
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>Marucco</t>
+          <t>Mini Derek / Mini derek</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="16">
       <c r="A33" s="25" t="inlineStr">
         <is>
-          <t>matheus</t>
+          <t>mito</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>Matheus</t>
+          <t>Mito</t>
         </is>
       </c>
       <c r="C33" s="26" t="n"/>
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="26" t="n"/>
-      <c r="F33" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="F33" s="25" t="n"/>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>matheus</t>
+          <t>Mito</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="16">
       <c r="A34" s="25" t="inlineStr">
         <is>
-          <t>merizi</t>
+          <t>nathan</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>Merizi GK</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="C34" s="26" t="n"/>
-      <c r="D34" s="26" t="inlineStr">
-        <is>
-          <t>GOL</t>
-        </is>
-      </c>
+      <c r="D34" s="26" t="n"/>
       <c r="E34" s="26" t="n"/>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -2376,65 +2388,69 @@
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>Merizi / Merizi GK / merizi</t>
+          <t>Nathan / nathan</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="16">
       <c r="A35" s="25" t="inlineStr">
         <is>
-          <t>miniderek</t>
+          <t>pairobson</t>
         </is>
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>Mini Derek</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="n"/>
+          <t>Pai Robson</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
       <c r="D35" s="26" t="n"/>
       <c r="E35" s="26" t="n"/>
-      <c r="F35" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="F35" s="25" t="n"/>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>Mini Derek / Mini derek</t>
+          <t>Pai Robson</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="16">
       <c r="A36" s="25" t="inlineStr">
         <is>
-          <t>mito</t>
+          <t>phelps</t>
         </is>
       </c>
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>Mito</t>
+          <t>Phelps</t>
         </is>
       </c>
       <c r="C36" s="26" t="n"/>
       <c r="D36" s="26" t="n"/>
       <c r="E36" s="26" t="n"/>
-      <c r="F36" s="25" t="n"/>
+      <c r="F36" s="25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>Mito</t>
+          <t>Felps / Phelps / phelps</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="16">
       <c r="A37" s="25" t="inlineStr">
         <is>
-          <t>nathan</t>
+          <t>pietro</t>
         </is>
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="C37" s="26" t="n"/>
@@ -2447,65 +2463,65 @@
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>Nathan / nathan</t>
+          <t>Pietro / pietro</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="16">
       <c r="A38" s="25" t="inlineStr">
         <is>
-          <t>pairobson</t>
+          <t>probst</t>
         </is>
       </c>
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>Pai Robson</t>
+          <t>Probst</t>
         </is>
       </c>
       <c r="C38" s="26" t="n"/>
       <c r="D38" s="26" t="n"/>
       <c r="E38" s="26" t="n"/>
-      <c r="F38" s="25" t="n"/>
+      <c r="F38" s="25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>Pai Robson</t>
+          <t>Probst / probst</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="16">
       <c r="A39" s="25" t="inlineStr">
         <is>
-          <t>phelps</t>
+          <t>robson</t>
         </is>
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>Phelps</t>
+          <t>Robson</t>
         </is>
       </c>
       <c r="C39" s="26" t="n"/>
       <c r="D39" s="26" t="n"/>
       <c r="E39" s="26" t="n"/>
-      <c r="F39" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="F39" s="25" t="n"/>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>Felps / Phelps / phelps</t>
+          <t>Robson</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="16">
       <c r="A40" s="25" t="inlineStr">
         <is>
-          <t>pietro</t>
+          <t>sograo</t>
         </is>
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Sograo</t>
         </is>
       </c>
       <c r="C40" s="26" t="n"/>
@@ -2518,19 +2534,19 @@
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>Pietro / pietro</t>
+          <t>sograo</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="16">
       <c r="A41" s="25" t="inlineStr">
         <is>
-          <t>probst</t>
+          <t>vicente</t>
         </is>
       </c>
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>Probst</t>
+          <t>Vicente</t>
         </is>
       </c>
       <c r="C41" s="26" t="n"/>
@@ -2543,40 +2559,44 @@
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>Probst / probst</t>
+          <t>vicente</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="16">
       <c r="A42" s="25" t="inlineStr">
         <is>
-          <t>robson</t>
+          <t>vitao</t>
         </is>
       </c>
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>Robson</t>
+          <t>Vitao</t>
         </is>
       </c>
       <c r="C42" s="26" t="n"/>
       <c r="D42" s="26" t="n"/>
       <c r="E42" s="26" t="n"/>
-      <c r="F42" s="25" t="n"/>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>Robson</t>
+          <t>Vitao / vitao</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="16">
       <c r="A43" s="25" t="inlineStr">
         <is>
-          <t>sograo</t>
+          <t>vitor</t>
         </is>
       </c>
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>Sograo</t>
+          <t>Vitor</t>
         </is>
       </c>
       <c r="C43" s="26" t="n"/>
@@ -2589,19 +2609,19 @@
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>sograo</t>
+          <t>gordo</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="16">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>vicente</t>
+          <t>zaga</t>
         </is>
       </c>
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>Vicente</t>
+          <t>Zaga</t>
         </is>
       </c>
       <c r="C44" s="26" t="n"/>
@@ -2614,102 +2634,14 @@
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>vicente</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="16">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>vitao</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="inlineStr">
-        <is>
-          <t>Vitao</t>
-        </is>
-      </c>
-      <c r="C45" s="26" t="n"/>
-      <c r="D45" s="26" t="n"/>
-      <c r="E45" s="26" t="n"/>
-      <c r="F45" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G45" s="25" t="inlineStr">
-        <is>
-          <t>Vitao / vitao</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="16">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>vitim</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="inlineStr">
-        <is>
-          <t>Vitim</t>
-        </is>
-      </c>
-      <c r="C46" s="26" t="n"/>
-      <c r="D46" s="26" t="n"/>
-      <c r="E46" s="26" t="n"/>
-      <c r="F46" s="25" t="n"/>
-      <c r="G46" s="25" t="inlineStr">
-        <is>
-          <t>Vitim</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="16">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>vitor</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="inlineStr">
-        <is>
-          <t>Vitor</t>
-        </is>
-      </c>
-      <c r="C47" s="26" t="n"/>
-      <c r="D47" s="26" t="n"/>
-      <c r="E47" s="26" t="n"/>
-      <c r="F47" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G47" s="25" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="16">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>zaga</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="inlineStr">
-        <is>
-          <t>Zaga</t>
-        </is>
-      </c>
-      <c r="C48" s="26" t="n"/>
-      <c r="D48" s="26" t="n"/>
-      <c r="E48" s="26" t="n"/>
-      <c r="F48" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G48" s="25" t="inlineStr">
-        <is>
           <t>Zaga / zaga</t>
         </is>
       </c>
     </row>
+    <row r="45" ht="15" customHeight="1" s="16"/>
+    <row r="46" ht="15" customHeight="1" s="16"/>
+    <row r="47" ht="15" customHeight="1" s="16"/>
+    <row r="48" ht="15" customHeight="1" s="16"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3933,7 +3865,7 @@
       </c>
       <c r="G4" s="26" t="n"/>
       <c r="H4" s="26" t="n"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3964,7 +3896,7 @@
       </c>
       <c r="G5" s="26" t="n"/>
       <c r="H5" s="26" t="n"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3995,7 +3927,7 @@
       </c>
       <c r="G6" s="26" t="n"/>
       <c r="H6" s="26" t="n"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4026,7 +3958,7 @@
       </c>
       <c r="G7" s="26" t="n"/>
       <c r="H7" s="26" t="n"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4057,7 +3989,7 @@
       </c>
       <c r="G8" s="26" t="n"/>
       <c r="H8" s="26" t="n"/>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4088,7 +4020,7 @@
       </c>
       <c r="G9" s="26" t="n"/>
       <c r="H9" s="26" t="n"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4102,7 +4034,7 @@
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>vitim</t>
+          <t>kretzer</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -4119,7 +4051,7 @@
       </c>
       <c r="G10" s="26" t="n"/>
       <c r="H10" s="26" t="n"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4150,7 +4082,7 @@
       </c>
       <c r="G11" s="26" t="n"/>
       <c r="H11" s="26" t="n"/>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4181,7 +4113,7 @@
       </c>
       <c r="G12" s="26" t="n"/>
       <c r="H12" s="26" t="n"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4212,7 +4144,7 @@
       </c>
       <c r="G13" s="26" t="n"/>
       <c r="H13" s="26" t="n"/>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4243,7 +4175,7 @@
       </c>
       <c r="G14" s="26" t="n"/>
       <c r="H14" s="26" t="n"/>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4274,7 +4206,7 @@
       </c>
       <c r="G15" s="26" t="n"/>
       <c r="H15" s="26" t="n"/>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4305,7 +4237,7 @@
       </c>
       <c r="G16" s="26" t="n"/>
       <c r="H16" s="26" t="n"/>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4336,7 +4268,7 @@
       </c>
       <c r="G17" s="26" t="n"/>
       <c r="H17" s="26" t="n"/>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4367,7 +4299,7 @@
       </c>
       <c r="G18" s="26" t="n"/>
       <c r="H18" s="26" t="n"/>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4398,7 +4330,7 @@
       </c>
       <c r="G19" s="26" t="n"/>
       <c r="H19" s="26" t="n"/>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4429,7 +4361,7 @@
       </c>
       <c r="G20" s="26" t="n"/>
       <c r="H20" s="26" t="n"/>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4460,7 +4392,7 @@
       </c>
       <c r="G21" s="26" t="n"/>
       <c r="H21" s="26" t="n"/>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4491,7 +4423,7 @@
       </c>
       <c r="G22" s="26" t="n"/>
       <c r="H22" s="26" t="n"/>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4522,7 +4454,7 @@
       </c>
       <c r="G23" s="26" t="n"/>
       <c r="H23" s="26" t="n"/>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4553,7 +4485,7 @@
       </c>
       <c r="G24" s="26" t="n"/>
       <c r="H24" s="26" t="n"/>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4584,7 +4516,7 @@
       </c>
       <c r="G25" s="26" t="n"/>
       <c r="H25" s="26" t="n"/>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4615,7 +4547,7 @@
       </c>
       <c r="G26" s="26" t="n"/>
       <c r="H26" s="26" t="n"/>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4629,7 +4561,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>bernardoc</t>
+          <t>correa</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
@@ -4646,7 +4578,7 @@
       </c>
       <c r="G27" s="26" t="n"/>
       <c r="H27" s="26" t="n"/>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4677,7 +4609,7 @@
       </c>
       <c r="G28" s="26" t="n"/>
       <c r="H28" s="26" t="n"/>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4708,7 +4640,7 @@
       </c>
       <c r="G29" s="26" t="n"/>
       <c r="H29" s="26" t="n"/>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4739,7 +4671,7 @@
       </c>
       <c r="G30" s="26" t="n"/>
       <c r="H30" s="26" t="n"/>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4770,7 +4702,7 @@
       </c>
       <c r="G31" s="26" t="n"/>
       <c r="H31" s="26" t="n"/>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4784,7 +4716,7 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>vitim</t>
+          <t>kretzer</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
@@ -4801,7 +4733,7 @@
       </c>
       <c r="G32" s="26" t="n"/>
       <c r="H32" s="26" t="n"/>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4832,7 +4764,7 @@
       </c>
       <c r="G33" s="26" t="n"/>
       <c r="H33" s="26" t="n"/>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4863,7 +4795,7 @@
       </c>
       <c r="G34" s="26" t="n"/>
       <c r="H34" s="26" t="n"/>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4877,7 +4809,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>bernardom</t>
+          <t>marucco</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
@@ -4894,7 +4826,7 @@
       </c>
       <c r="G35" s="26" t="n"/>
       <c r="H35" s="26" t="n"/>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4925,7 +4857,7 @@
       </c>
       <c r="G36" s="26" t="n"/>
       <c r="H36" s="26" t="n"/>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4956,7 +4888,7 @@
       </c>
       <c r="G37" s="26" t="n"/>
       <c r="H37" s="26" t="n"/>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4987,7 +4919,7 @@
       </c>
       <c r="G38" s="26" t="n"/>
       <c r="H38" s="26" t="n"/>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5018,7 +4950,7 @@
       </c>
       <c r="G39" s="26" t="n"/>
       <c r="H39" s="26" t="n"/>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5049,7 +4981,7 @@
       </c>
       <c r="G40" s="26" t="n"/>
       <c r="H40" s="26" t="n"/>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5063,7 +4995,7 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>gordo</t>
+          <t>vitor</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
@@ -5080,7 +5012,7 @@
       </c>
       <c r="G41" s="26" t="n"/>
       <c r="H41" s="26" t="n"/>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5111,7 +5043,7 @@
       </c>
       <c r="G42" s="26" t="n"/>
       <c r="H42" s="26" t="n"/>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5142,7 +5074,7 @@
       </c>
       <c r="G43" s="26" t="n"/>
       <c r="H43" s="26" t="n"/>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5173,7 +5105,7 @@
       </c>
       <c r="G44" s="26" t="n"/>
       <c r="H44" s="26" t="n"/>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5204,7 +5136,7 @@
       </c>
       <c r="G45" s="26" t="n"/>
       <c r="H45" s="26" t="n"/>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5235,7 +5167,7 @@
       </c>
       <c r="G46" s="26" t="n"/>
       <c r="H46" s="26" t="n"/>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5266,7 +5198,7 @@
       </c>
       <c r="G47" s="26" t="n"/>
       <c r="H47" s="26" t="n"/>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5280,7 +5212,7 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>vitim</t>
+          <t>kretzer</t>
         </is>
       </c>
       <c r="C48" s="27" t="inlineStr">
@@ -5297,7 +5229,7 @@
       </c>
       <c r="G48" s="26" t="n"/>
       <c r="H48" s="26" t="n"/>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5328,7 +5260,7 @@
       </c>
       <c r="G49" s="26" t="n"/>
       <c r="H49" s="26" t="n"/>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5359,7 +5291,7 @@
       </c>
       <c r="G50" s="26" t="n"/>
       <c r="H50" s="26" t="n"/>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5390,7 +5322,7 @@
       </c>
       <c r="G51" s="26" t="n"/>
       <c r="H51" s="26" t="n"/>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5425,7 +5357,7 @@
       </c>
       <c r="G52" s="26" t="n"/>
       <c r="H52" s="26" t="n"/>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5460,7 +5392,7 @@
       </c>
       <c r="G53" s="26" t="n"/>
       <c r="H53" s="26" t="n"/>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5495,7 +5427,7 @@
       </c>
       <c r="G54" s="26" t="n"/>
       <c r="H54" s="26" t="n"/>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5530,7 +5462,7 @@
       </c>
       <c r="G55" s="26" t="n"/>
       <c r="H55" s="26" t="n"/>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5565,7 +5497,7 @@
       </c>
       <c r="G56" s="26" t="n"/>
       <c r="H56" s="26" t="n"/>
-      <c r="J56" t="inlineStr">
+      <c r="J56" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5600,7 +5532,7 @@
       </c>
       <c r="G57" s="26" t="n"/>
       <c r="H57" s="26" t="n"/>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5635,7 +5567,7 @@
       </c>
       <c r="G58" s="26" t="n"/>
       <c r="H58" s="26" t="n"/>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5670,7 +5602,7 @@
       </c>
       <c r="G59" s="26" t="n"/>
       <c r="H59" s="26" t="n"/>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5705,7 +5637,7 @@
       </c>
       <c r="G60" s="26" t="n"/>
       <c r="H60" s="26" t="n"/>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5719,7 +5651,7 @@
       </c>
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>bernardom</t>
+          <t>marucco</t>
         </is>
       </c>
       <c r="C61" s="25" t="inlineStr">
@@ -5736,7 +5668,7 @@
       </c>
       <c r="G61" s="26" t="n"/>
       <c r="H61" s="26" t="n"/>
-      <c r="J61" t="inlineStr">
+      <c r="J61" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5771,7 +5703,7 @@
       </c>
       <c r="G62" s="26" t="n"/>
       <c r="H62" s="26" t="n"/>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5806,7 +5738,7 @@
       </c>
       <c r="G63" s="26" t="n"/>
       <c r="H63" s="26" t="n"/>
-      <c r="J63" t="inlineStr">
+      <c r="J63" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5841,7 +5773,7 @@
       </c>
       <c r="G64" s="26" t="n"/>
       <c r="H64" s="26" t="n"/>
-      <c r="J64" t="inlineStr">
+      <c r="J64" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5876,7 +5808,7 @@
       </c>
       <c r="G65" s="26" t="n"/>
       <c r="H65" s="26" t="n"/>
-      <c r="J65" t="inlineStr">
+      <c r="J65" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5911,7 +5843,7 @@
       </c>
       <c r="G66" s="26" t="n"/>
       <c r="H66" s="26" t="n"/>
-      <c r="J66" t="inlineStr">
+      <c r="J66" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5946,7 +5878,7 @@
       </c>
       <c r="G67" s="26" t="n"/>
       <c r="H67" s="26" t="n"/>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -5981,7 +5913,7 @@
       </c>
       <c r="G68" s="26" t="n"/>
       <c r="H68" s="26" t="n"/>
-      <c r="J68" t="inlineStr">
+      <c r="J68" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6016,7 +5948,7 @@
       </c>
       <c r="G69" s="26" t="n"/>
       <c r="H69" s="26" t="n"/>
-      <c r="J69" t="inlineStr">
+      <c r="J69" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6051,7 +5983,7 @@
       </c>
       <c r="G70" s="26" t="n"/>
       <c r="H70" s="26" t="n"/>
-      <c r="J70" t="inlineStr">
+      <c r="J70" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6065,7 +5997,7 @@
       </c>
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>bernardoc</t>
+          <t>correa</t>
         </is>
       </c>
       <c r="C71" s="25" t="inlineStr">
@@ -6082,7 +6014,7 @@
       </c>
       <c r="G71" s="26" t="n"/>
       <c r="H71" s="26" t="n"/>
-      <c r="J71" t="inlineStr">
+      <c r="J71" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6117,7 +6049,7 @@
       </c>
       <c r="G72" s="26" t="n"/>
       <c r="H72" s="26" t="n"/>
-      <c r="J72" t="inlineStr">
+      <c r="J72" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6152,7 +6084,7 @@
       </c>
       <c r="G73" s="26" t="n"/>
       <c r="H73" s="26" t="n"/>
-      <c r="J73" t="inlineStr">
+      <c r="J73" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6187,7 +6119,7 @@
       </c>
       <c r="G74" s="26" t="n"/>
       <c r="H74" s="26" t="n"/>
-      <c r="J74" t="inlineStr">
+      <c r="J74" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6222,7 +6154,7 @@
       </c>
       <c r="G75" s="26" t="n"/>
       <c r="H75" s="26" t="n"/>
-      <c r="J75" t="inlineStr">
+      <c r="J75" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6257,7 +6189,7 @@
       </c>
       <c r="G76" s="26" t="n"/>
       <c r="H76" s="26" t="n"/>
-      <c r="J76" t="inlineStr">
+      <c r="J76" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6292,7 +6224,7 @@
       </c>
       <c r="G77" s="26" t="n"/>
       <c r="H77" s="26" t="n"/>
-      <c r="J77" t="inlineStr">
+      <c r="J77" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6327,7 +6259,7 @@
       </c>
       <c r="G78" s="26" t="n"/>
       <c r="H78" s="26" t="n"/>
-      <c r="J78" t="inlineStr">
+      <c r="J78" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6362,7 +6294,7 @@
       </c>
       <c r="G79" s="26" t="n"/>
       <c r="H79" s="26" t="n"/>
-      <c r="J79" t="inlineStr">
+      <c r="J79" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6397,7 +6329,7 @@
       </c>
       <c r="G80" s="26" t="n"/>
       <c r="H80" s="26" t="n"/>
-      <c r="J80" t="inlineStr">
+      <c r="J80" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6432,7 +6364,7 @@
       </c>
       <c r="G81" s="26" t="n"/>
       <c r="H81" s="26" t="n"/>
-      <c r="J81" t="inlineStr">
+      <c r="J81" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6467,7 +6399,7 @@
       </c>
       <c r="G82" s="26" t="n"/>
       <c r="H82" s="26" t="n"/>
-      <c r="J82" t="inlineStr">
+      <c r="J82" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6502,7 +6434,7 @@
       </c>
       <c r="G83" s="26" t="n"/>
       <c r="H83" s="26" t="n"/>
-      <c r="J83" t="inlineStr">
+      <c r="J83" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6537,7 +6469,7 @@
       </c>
       <c r="G84" s="26" t="n"/>
       <c r="H84" s="26" t="n"/>
-      <c r="J84" t="inlineStr">
+      <c r="J84" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6572,7 +6504,7 @@
       </c>
       <c r="G85" s="26" t="n"/>
       <c r="H85" s="26" t="n"/>
-      <c r="J85" t="inlineStr">
+      <c r="J85" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6607,7 +6539,7 @@
       </c>
       <c r="G86" s="26" t="n"/>
       <c r="H86" s="26" t="n"/>
-      <c r="J86" t="inlineStr">
+      <c r="J86" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6642,7 +6574,7 @@
       </c>
       <c r="G87" s="26" t="n"/>
       <c r="H87" s="26" t="n"/>
-      <c r="J87" t="inlineStr">
+      <c r="J87" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6677,7 +6609,7 @@
       </c>
       <c r="G88" s="26" t="n"/>
       <c r="H88" s="26" t="n"/>
-      <c r="J88" t="inlineStr">
+      <c r="J88" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6712,7 +6644,7 @@
       </c>
       <c r="G89" s="26" t="n"/>
       <c r="H89" s="26" t="n"/>
-      <c r="J89" t="inlineStr">
+      <c r="J89" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6747,7 +6679,7 @@
       </c>
       <c r="G90" s="26" t="n"/>
       <c r="H90" s="26" t="n"/>
-      <c r="J90" t="inlineStr">
+      <c r="J90" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6782,7 +6714,7 @@
       </c>
       <c r="G91" s="26" t="n"/>
       <c r="H91" s="26" t="n"/>
-      <c r="J91" t="inlineStr">
+      <c r="J91" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6817,7 +6749,7 @@
       </c>
       <c r="G92" s="26" t="n"/>
       <c r="H92" s="26" t="n"/>
-      <c r="J92" t="inlineStr">
+      <c r="J92" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6852,7 +6784,7 @@
       </c>
       <c r="G93" s="26" t="n"/>
       <c r="H93" s="26" t="n"/>
-      <c r="J93" t="inlineStr">
+      <c r="J93" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6887,7 +6819,7 @@
       </c>
       <c r="G94" s="26" t="n"/>
       <c r="H94" s="26" t="n"/>
-      <c r="J94" t="inlineStr">
+      <c r="J94" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6922,7 +6854,7 @@
       </c>
       <c r="G95" s="26" t="n"/>
       <c r="H95" s="26" t="n"/>
-      <c r="J95" t="inlineStr">
+      <c r="J95" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6957,7 +6889,7 @@
       </c>
       <c r="G96" s="26" t="n"/>
       <c r="H96" s="26" t="n"/>
-      <c r="J96" t="inlineStr">
+      <c r="J96" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -6992,7 +6924,7 @@
       </c>
       <c r="G97" s="26" t="n"/>
       <c r="H97" s="26" t="n"/>
-      <c r="J97" t="inlineStr">
+      <c r="J97" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7006,7 +6938,7 @@
       </c>
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>bernardom</t>
+          <t>marucco</t>
         </is>
       </c>
       <c r="C98" s="25" t="inlineStr">
@@ -7023,7 +6955,7 @@
       </c>
       <c r="G98" s="26" t="n"/>
       <c r="H98" s="26" t="n"/>
-      <c r="J98" t="inlineStr">
+      <c r="J98" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7058,7 +6990,7 @@
       </c>
       <c r="G99" s="26" t="n"/>
       <c r="H99" s="26" t="n"/>
-      <c r="J99" t="inlineStr">
+      <c r="J99" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7093,7 +7025,7 @@
       </c>
       <c r="G100" s="26" t="n"/>
       <c r="H100" s="26" t="n"/>
-      <c r="J100" t="inlineStr">
+      <c r="J100" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7128,7 +7060,7 @@
       </c>
       <c r="G101" s="26" t="n"/>
       <c r="H101" s="26" t="n"/>
-      <c r="J101" t="inlineStr">
+      <c r="J101" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7163,7 +7095,7 @@
       </c>
       <c r="G102" s="26" t="n"/>
       <c r="H102" s="26" t="n"/>
-      <c r="J102" t="inlineStr">
+      <c r="J102" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7198,7 +7130,7 @@
       </c>
       <c r="G103" s="26" t="n"/>
       <c r="H103" s="26" t="n"/>
-      <c r="J103" t="inlineStr">
+      <c r="J103" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7233,7 +7165,7 @@
       </c>
       <c r="G104" s="26" t="n"/>
       <c r="H104" s="26" t="n"/>
-      <c r="J104" t="inlineStr">
+      <c r="J104" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7268,7 +7200,7 @@
       </c>
       <c r="G105" s="26" t="n"/>
       <c r="H105" s="26" t="n"/>
-      <c r="J105" t="inlineStr">
+      <c r="J105" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7303,7 +7235,7 @@
       </c>
       <c r="G106" s="26" t="n"/>
       <c r="H106" s="26" t="n"/>
-      <c r="J106" t="inlineStr">
+      <c r="J106" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7338,7 +7270,7 @@
       </c>
       <c r="G107" s="26" t="n"/>
       <c r="H107" s="26" t="n"/>
-      <c r="J107" t="inlineStr">
+      <c r="J107" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7352,7 +7284,7 @@
       </c>
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>bernardoc</t>
+          <t>correa</t>
         </is>
       </c>
       <c r="C108" s="25" t="inlineStr">
@@ -7369,7 +7301,7 @@
       </c>
       <c r="G108" s="26" t="n"/>
       <c r="H108" s="26" t="n"/>
-      <c r="J108" t="inlineStr">
+      <c r="J108" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7404,7 +7336,7 @@
       </c>
       <c r="G109" s="26" t="n"/>
       <c r="H109" s="26" t="n"/>
-      <c r="J109" t="inlineStr">
+      <c r="J109" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7439,7 +7371,7 @@
       </c>
       <c r="G110" s="26" t="n"/>
       <c r="H110" s="26" t="n"/>
-      <c r="J110" t="inlineStr">
+      <c r="J110" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7474,7 +7406,7 @@
       </c>
       <c r="G111" s="26" t="n"/>
       <c r="H111" s="26" t="n"/>
-      <c r="J111" t="inlineStr">
+      <c r="J111" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7509,7 +7441,7 @@
       </c>
       <c r="G112" s="26" t="n"/>
       <c r="H112" s="26" t="n"/>
-      <c r="J112" t="inlineStr">
+      <c r="J112" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7544,7 +7476,7 @@
       </c>
       <c r="G113" s="26" t="n"/>
       <c r="H113" s="26" t="n"/>
-      <c r="J113" t="inlineStr">
+      <c r="J113" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7579,7 +7511,7 @@
       </c>
       <c r="G114" s="26" t="n"/>
       <c r="H114" s="26" t="n"/>
-      <c r="J114" t="inlineStr">
+      <c r="J114" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7614,7 +7546,7 @@
       </c>
       <c r="G115" s="26" t="n"/>
       <c r="H115" s="26" t="n"/>
-      <c r="J115" t="inlineStr">
+      <c r="J115" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7649,7 +7581,7 @@
       </c>
       <c r="G116" s="26" t="n"/>
       <c r="H116" s="26" t="n"/>
-      <c r="J116" t="inlineStr">
+      <c r="J116" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7684,7 +7616,7 @@
       </c>
       <c r="G117" s="26" t="n"/>
       <c r="H117" s="26" t="n"/>
-      <c r="J117" t="inlineStr">
+      <c r="J117" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7719,7 +7651,7 @@
       </c>
       <c r="G118" s="26" t="n"/>
       <c r="H118" s="26" t="n"/>
-      <c r="J118" t="inlineStr">
+      <c r="J118" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7754,7 +7686,7 @@
       </c>
       <c r="G119" s="26" t="n"/>
       <c r="H119" s="26" t="n"/>
-      <c r="J119" t="inlineStr">
+      <c r="J119" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7789,7 +7721,7 @@
       </c>
       <c r="G120" s="26" t="n"/>
       <c r="H120" s="26" t="n"/>
-      <c r="J120" t="inlineStr">
+      <c r="J120" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7803,7 +7735,7 @@
       </c>
       <c r="B121" s="27" t="inlineStr">
         <is>
-          <t>gordo</t>
+          <t>vitor</t>
         </is>
       </c>
       <c r="C121" s="27" t="inlineStr">
@@ -7824,7 +7756,7 @@
       </c>
       <c r="G121" s="26" t="n"/>
       <c r="H121" s="26" t="n"/>
-      <c r="J121" t="inlineStr">
+      <c r="J121" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7859,7 +7791,7 @@
       </c>
       <c r="G122" s="26" t="n"/>
       <c r="H122" s="26" t="n"/>
-      <c r="J122" t="inlineStr">
+      <c r="J122" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7894,7 +7826,7 @@
       </c>
       <c r="G123" s="26" t="n"/>
       <c r="H123" s="26" t="n"/>
-      <c r="J123" t="inlineStr">
+      <c r="J123" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7929,7 +7861,7 @@
       </c>
       <c r="G124" s="26" t="n"/>
       <c r="H124" s="26" t="n"/>
-      <c r="J124" t="inlineStr">
+      <c r="J124" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7964,7 +7896,7 @@
       </c>
       <c r="G125" s="26" t="n"/>
       <c r="H125" s="26" t="n"/>
-      <c r="J125" t="inlineStr">
+      <c r="J125" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -7999,7 +7931,7 @@
       </c>
       <c r="G126" s="26" t="n"/>
       <c r="H126" s="26" t="n"/>
-      <c r="J126" t="inlineStr">
+      <c r="J126" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8034,7 +7966,7 @@
       </c>
       <c r="G127" s="26" t="n"/>
       <c r="H127" s="26" t="n"/>
-      <c r="J127" t="inlineStr">
+      <c r="J127" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8069,7 +8001,7 @@
       </c>
       <c r="G128" s="26" t="n"/>
       <c r="H128" s="26" t="n"/>
-      <c r="J128" t="inlineStr">
+      <c r="J128" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8104,7 +8036,7 @@
       </c>
       <c r="G129" s="26" t="n"/>
       <c r="H129" s="26" t="n"/>
-      <c r="J129" t="inlineStr">
+      <c r="J129" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8139,7 +8071,7 @@
       </c>
       <c r="G130" s="26" t="n"/>
       <c r="H130" s="26" t="n"/>
-      <c r="J130" t="inlineStr">
+      <c r="J130" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8174,7 +8106,7 @@
       </c>
       <c r="G131" s="26" t="n"/>
       <c r="H131" s="26" t="n"/>
-      <c r="J131" t="inlineStr">
+      <c r="J131" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8209,7 +8141,7 @@
       </c>
       <c r="G132" s="26" t="n"/>
       <c r="H132" s="26" t="n"/>
-      <c r="J132" t="inlineStr">
+      <c r="J132" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8244,7 +8176,7 @@
       </c>
       <c r="G133" s="26" t="n"/>
       <c r="H133" s="26" t="n"/>
-      <c r="J133" t="inlineStr">
+      <c r="J133" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8279,7 +8211,7 @@
       </c>
       <c r="G134" s="26" t="n"/>
       <c r="H134" s="26" t="n"/>
-      <c r="J134" t="inlineStr">
+      <c r="J134" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8314,7 +8246,7 @@
       </c>
       <c r="G135" s="26" t="n"/>
       <c r="H135" s="26" t="n"/>
-      <c r="J135" t="inlineStr">
+      <c r="J135" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8349,7 +8281,7 @@
       </c>
       <c r="G136" s="26" t="n"/>
       <c r="H136" s="26" t="n"/>
-      <c r="J136" t="inlineStr">
+      <c r="J136" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8384,7 +8316,7 @@
       </c>
       <c r="G137" s="26" t="n"/>
       <c r="H137" s="26" t="n"/>
-      <c r="J137" t="inlineStr">
+      <c r="J137" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8419,7 +8351,7 @@
       </c>
       <c r="G138" s="26" t="n"/>
       <c r="H138" s="26" t="n"/>
-      <c r="J138" t="inlineStr">
+      <c r="J138" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8454,7 +8386,7 @@
       </c>
       <c r="G139" s="26" t="n"/>
       <c r="H139" s="26" t="n"/>
-      <c r="J139" t="inlineStr">
+      <c r="J139" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8489,7 +8421,7 @@
       </c>
       <c r="G140" s="26" t="n"/>
       <c r="H140" s="26" t="n"/>
-      <c r="J140" t="inlineStr">
+      <c r="J140" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8524,7 +8456,7 @@
       </c>
       <c r="G141" s="26" t="n"/>
       <c r="H141" s="26" t="n"/>
-      <c r="J141" t="inlineStr">
+      <c r="J141" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8538,7 +8470,7 @@
       </c>
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>gordo</t>
+          <t>vitor</t>
         </is>
       </c>
       <c r="C142" s="25" t="inlineStr">
@@ -8559,7 +8491,7 @@
       </c>
       <c r="G142" s="26" t="n"/>
       <c r="H142" s="26" t="n"/>
-      <c r="J142" t="inlineStr">
+      <c r="J142" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8594,7 +8526,7 @@
       </c>
       <c r="G143" s="26" t="n"/>
       <c r="H143" s="26" t="n"/>
-      <c r="J143" t="inlineStr">
+      <c r="J143" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8629,7 +8561,7 @@
       </c>
       <c r="G144" s="26" t="n"/>
       <c r="H144" s="26" t="n"/>
-      <c r="J144" t="inlineStr">
+      <c r="J144" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8664,7 +8596,7 @@
       </c>
       <c r="G145" s="26" t="n"/>
       <c r="H145" s="26" t="n"/>
-      <c r="J145" t="inlineStr">
+      <c r="J145" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8699,7 +8631,7 @@
       </c>
       <c r="G146" s="26" t="n"/>
       <c r="H146" s="26" t="n"/>
-      <c r="J146" t="inlineStr">
+      <c r="J146" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8734,7 +8666,7 @@
       </c>
       <c r="G147" s="26" t="n"/>
       <c r="H147" s="26" t="n"/>
-      <c r="J147" t="inlineStr">
+      <c r="J147" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8769,7 +8701,7 @@
       </c>
       <c r="G148" s="26" t="n"/>
       <c r="H148" s="26" t="n"/>
-      <c r="J148" t="inlineStr">
+      <c r="J148" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8804,7 +8736,7 @@
       </c>
       <c r="G149" s="26" t="n"/>
       <c r="H149" s="26" t="n"/>
-      <c r="J149" t="inlineStr">
+      <c r="J149" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8839,7 +8771,7 @@
       </c>
       <c r="G150" s="26" t="n"/>
       <c r="H150" s="26" t="n"/>
-      <c r="J150" t="inlineStr">
+      <c r="J150" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8874,7 +8806,7 @@
       </c>
       <c r="G151" s="26" t="n"/>
       <c r="H151" s="26" t="n"/>
-      <c r="J151" t="inlineStr">
+      <c r="J151" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8909,7 +8841,7 @@
       </c>
       <c r="G152" s="26" t="n"/>
       <c r="H152" s="26" t="n"/>
-      <c r="J152" t="inlineStr">
+      <c r="J152" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8944,7 +8876,7 @@
       </c>
       <c r="G153" s="26" t="n"/>
       <c r="H153" s="26" t="n"/>
-      <c r="J153" t="inlineStr">
+      <c r="J153" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -8979,7 +8911,7 @@
       </c>
       <c r="G154" s="26" t="n"/>
       <c r="H154" s="26" t="n"/>
-      <c r="J154" t="inlineStr">
+      <c r="J154" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9014,7 +8946,7 @@
       </c>
       <c r="G155" s="26" t="n"/>
       <c r="H155" s="26" t="n"/>
-      <c r="J155" t="inlineStr">
+      <c r="J155" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9049,7 +8981,7 @@
       </c>
       <c r="G156" s="26" t="n"/>
       <c r="H156" s="26" t="n"/>
-      <c r="J156" t="inlineStr">
+      <c r="J156" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9084,7 +9016,7 @@
       </c>
       <c r="G157" s="26" t="n"/>
       <c r="H157" s="26" t="n"/>
-      <c r="J157" t="inlineStr">
+      <c r="J157" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9119,7 +9051,7 @@
       </c>
       <c r="G158" s="26" t="n"/>
       <c r="H158" s="26" t="n"/>
-      <c r="J158" t="inlineStr">
+      <c r="J158" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9157,7 +9089,7 @@
       <c r="I159" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J159" t="inlineStr">
+      <c r="J159" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9192,7 +9124,7 @@
       </c>
       <c r="G160" s="26" t="n"/>
       <c r="H160" s="26" t="n"/>
-      <c r="J160" t="inlineStr">
+      <c r="J160" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9227,7 +9159,7 @@
       </c>
       <c r="G161" s="26" t="n"/>
       <c r="H161" s="26" t="n"/>
-      <c r="J161" t="inlineStr">
+      <c r="J161" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9262,7 +9194,7 @@
       </c>
       <c r="G162" s="26" t="n"/>
       <c r="H162" s="26" t="n"/>
-      <c r="J162" t="inlineStr">
+      <c r="J162" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9297,7 +9229,7 @@
       </c>
       <c r="G163" s="26" t="n"/>
       <c r="H163" s="26" t="n"/>
-      <c r="J163" t="inlineStr">
+      <c r="J163" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9332,7 +9264,7 @@
       </c>
       <c r="G164" s="26" t="n"/>
       <c r="H164" s="26" t="n"/>
-      <c r="J164" t="inlineStr">
+      <c r="J164" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9367,7 +9299,7 @@
       </c>
       <c r="G165" s="26" t="n"/>
       <c r="H165" s="26" t="n"/>
-      <c r="J165" t="inlineStr">
+      <c r="J165" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9402,7 +9334,7 @@
       </c>
       <c r="G166" s="26" t="n"/>
       <c r="H166" s="26" t="n"/>
-      <c r="J166" t="inlineStr">
+      <c r="J166" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9437,7 +9369,7 @@
       </c>
       <c r="G167" s="26" t="n"/>
       <c r="H167" s="26" t="n"/>
-      <c r="J167" t="inlineStr">
+      <c r="J167" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9472,7 +9404,7 @@
       </c>
       <c r="G168" s="26" t="n"/>
       <c r="H168" s="26" t="n"/>
-      <c r="J168" t="inlineStr">
+      <c r="J168" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9507,7 +9439,7 @@
       </c>
       <c r="G169" s="26" t="n"/>
       <c r="H169" s="26" t="n"/>
-      <c r="J169" t="inlineStr">
+      <c r="J169" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9542,7 +9474,7 @@
       </c>
       <c r="G170" s="26" t="n"/>
       <c r="H170" s="26" t="n"/>
-      <c r="J170" t="inlineStr">
+      <c r="J170" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9577,7 +9509,7 @@
       </c>
       <c r="G171" s="26" t="n"/>
       <c r="H171" s="26" t="n"/>
-      <c r="J171" t="inlineStr">
+      <c r="J171" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9612,7 +9544,7 @@
       </c>
       <c r="G172" s="26" t="n"/>
       <c r="H172" s="26" t="n"/>
-      <c r="J172" t="inlineStr">
+      <c r="J172" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9647,7 +9579,7 @@
       </c>
       <c r="G173" s="26" t="n"/>
       <c r="H173" s="26" t="n"/>
-      <c r="J173" t="inlineStr">
+      <c r="J173" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9682,7 +9614,7 @@
       </c>
       <c r="G174" s="26" t="n"/>
       <c r="H174" s="26" t="n"/>
-      <c r="J174" t="inlineStr">
+      <c r="J174" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9717,7 +9649,7 @@
       </c>
       <c r="G175" s="26" t="n"/>
       <c r="H175" s="26" t="n"/>
-      <c r="J175" t="inlineStr">
+      <c r="J175" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9752,7 +9684,7 @@
       </c>
       <c r="G176" s="26" t="n"/>
       <c r="H176" s="26" t="n"/>
-      <c r="J176" t="inlineStr">
+      <c r="J176" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9787,7 +9719,7 @@
       </c>
       <c r="G177" s="26" t="n"/>
       <c r="H177" s="26" t="n"/>
-      <c r="J177" t="inlineStr">
+      <c r="J177" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9822,7 +9754,7 @@
       </c>
       <c r="G178" s="26" t="n"/>
       <c r="H178" s="26" t="n"/>
-      <c r="J178" t="inlineStr">
+      <c r="J178" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9857,7 +9789,7 @@
       </c>
       <c r="G179" s="26" t="n"/>
       <c r="H179" s="26" t="n"/>
-      <c r="J179" t="inlineStr">
+      <c r="J179" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9892,7 +9824,7 @@
       </c>
       <c r="G180" s="26" t="n"/>
       <c r="H180" s="26" t="n"/>
-      <c r="J180" t="inlineStr">
+      <c r="J180" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9927,7 +9859,7 @@
       </c>
       <c r="G181" s="26" t="n"/>
       <c r="H181" s="26" t="n"/>
-      <c r="J181" t="inlineStr">
+      <c r="J181" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9962,7 +9894,7 @@
       </c>
       <c r="G182" s="26" t="n"/>
       <c r="H182" s="26" t="n"/>
-      <c r="J182" t="inlineStr">
+      <c r="J182" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -9997,7 +9929,7 @@
       </c>
       <c r="G183" s="26" t="n"/>
       <c r="H183" s="26" t="n"/>
-      <c r="J183" t="inlineStr">
+      <c r="J183" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10032,7 +9964,7 @@
       </c>
       <c r="G184" s="26" t="n"/>
       <c r="H184" s="26" t="n"/>
-      <c r="J184" t="inlineStr">
+      <c r="J184" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10067,7 +9999,7 @@
       </c>
       <c r="G185" s="26" t="n"/>
       <c r="H185" s="26" t="n"/>
-      <c r="J185" t="inlineStr">
+      <c r="J185" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10102,7 +10034,7 @@
       </c>
       <c r="G186" s="26" t="n"/>
       <c r="H186" s="26" t="n"/>
-      <c r="J186" t="inlineStr">
+      <c r="J186" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10137,7 +10069,7 @@
       </c>
       <c r="G187" s="26" t="n"/>
       <c r="H187" s="26" t="n"/>
-      <c r="J187" t="inlineStr">
+      <c r="J187" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10172,7 +10104,7 @@
       </c>
       <c r="G188" s="26" t="n"/>
       <c r="H188" s="26" t="n"/>
-      <c r="J188" t="inlineStr">
+      <c r="J188" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10186,7 +10118,7 @@
       </c>
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>gordo</t>
+          <t>vitor</t>
         </is>
       </c>
       <c r="C189" s="25" t="inlineStr">
@@ -10207,7 +10139,7 @@
       </c>
       <c r="G189" s="26" t="n"/>
       <c r="H189" s="26" t="n"/>
-      <c r="J189" t="inlineStr">
+      <c r="J189" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10242,7 +10174,7 @@
       </c>
       <c r="G190" s="26" t="n"/>
       <c r="H190" s="26" t="n"/>
-      <c r="J190" t="inlineStr">
+      <c r="J190" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10277,7 +10209,7 @@
       </c>
       <c r="G191" s="26" t="n"/>
       <c r="H191" s="26" t="n"/>
-      <c r="J191" t="inlineStr">
+      <c r="J191" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10312,7 +10244,7 @@
       </c>
       <c r="G192" s="26" t="n"/>
       <c r="H192" s="26" t="n"/>
-      <c r="J192" t="inlineStr">
+      <c r="J192" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10347,7 +10279,7 @@
       </c>
       <c r="G193" s="26" t="n"/>
       <c r="H193" s="26" t="n"/>
-      <c r="J193" t="inlineStr">
+      <c r="J193" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10382,7 +10314,7 @@
       </c>
       <c r="G194" s="26" t="n"/>
       <c r="H194" s="26" t="n"/>
-      <c r="J194" t="inlineStr">
+      <c r="J194" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10417,7 +10349,7 @@
       </c>
       <c r="G195" s="26" t="n"/>
       <c r="H195" s="26" t="n"/>
-      <c r="J195" t="inlineStr">
+      <c r="J195" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10452,7 +10384,7 @@
       </c>
       <c r="G196" s="26" t="n"/>
       <c r="H196" s="26" t="n"/>
-      <c r="J196" t="inlineStr">
+      <c r="J196" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10487,7 +10419,7 @@
       </c>
       <c r="G197" s="26" t="n"/>
       <c r="H197" s="26" t="n"/>
-      <c r="J197" t="inlineStr">
+      <c r="J197" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10522,7 +10454,7 @@
       </c>
       <c r="G198" s="26" t="n"/>
       <c r="H198" s="26" t="n"/>
-      <c r="J198" t="inlineStr">
+      <c r="J198" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10557,7 +10489,7 @@
       </c>
       <c r="G199" s="26" t="n"/>
       <c r="H199" s="26" t="n"/>
-      <c r="J199" t="inlineStr">
+      <c r="J199" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10592,7 +10524,7 @@
       </c>
       <c r="G200" s="26" t="n"/>
       <c r="H200" s="26" t="n"/>
-      <c r="J200" t="inlineStr">
+      <c r="J200" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10627,7 +10559,7 @@
       </c>
       <c r="G201" s="26" t="n"/>
       <c r="H201" s="26" t="n"/>
-      <c r="J201" t="inlineStr">
+      <c r="J201" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10662,7 +10594,7 @@
       </c>
       <c r="G202" s="26" t="n"/>
       <c r="H202" s="26" t="n"/>
-      <c r="J202" t="inlineStr">
+      <c r="J202" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10697,7 +10629,7 @@
       </c>
       <c r="G203" s="26" t="n"/>
       <c r="H203" s="26" t="n"/>
-      <c r="J203" t="inlineStr">
+      <c r="J203" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10732,7 +10664,7 @@
       </c>
       <c r="G204" s="26" t="n"/>
       <c r="H204" s="26" t="n"/>
-      <c r="J204" t="inlineStr">
+      <c r="J204" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10767,7 +10699,7 @@
       </c>
       <c r="G205" s="26" t="n"/>
       <c r="H205" s="26" t="n"/>
-      <c r="J205" t="inlineStr">
+      <c r="J205" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10802,7 +10734,7 @@
       </c>
       <c r="G206" s="26" t="n"/>
       <c r="H206" s="26" t="n"/>
-      <c r="J206" t="inlineStr">
+      <c r="J206" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10837,7 +10769,7 @@
       </c>
       <c r="G207" s="26" t="n"/>
       <c r="H207" s="26" t="n"/>
-      <c r="J207" t="inlineStr">
+      <c r="J207" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10872,7 +10804,7 @@
       </c>
       <c r="G208" s="26" t="n"/>
       <c r="H208" s="26" t="n"/>
-      <c r="J208" t="inlineStr">
+      <c r="J208" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10907,7 +10839,7 @@
       </c>
       <c r="G209" s="26" t="n"/>
       <c r="H209" s="26" t="n"/>
-      <c r="J209" t="inlineStr">
+      <c r="J209" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10942,7 +10874,7 @@
       </c>
       <c r="G210" s="26" t="n"/>
       <c r="H210" s="26" t="n"/>
-      <c r="J210" t="inlineStr">
+      <c r="J210" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -10977,7 +10909,7 @@
       </c>
       <c r="G211" s="26" t="n"/>
       <c r="H211" s="26" t="n"/>
-      <c r="J211" t="inlineStr">
+      <c r="J211" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11012,7 +10944,7 @@
       </c>
       <c r="G212" s="26" t="n"/>
       <c r="H212" s="26" t="n"/>
-      <c r="J212" t="inlineStr">
+      <c r="J212" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11047,7 +10979,7 @@
       </c>
       <c r="G213" s="26" t="n"/>
       <c r="H213" s="26" t="n"/>
-      <c r="J213" t="inlineStr">
+      <c r="J213" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11082,7 +11014,7 @@
       </c>
       <c r="G214" s="26" t="n"/>
       <c r="H214" s="26" t="n"/>
-      <c r="J214" t="inlineStr">
+      <c r="J214" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11117,7 +11049,7 @@
       </c>
       <c r="G215" s="26" t="n"/>
       <c r="H215" s="26" t="n"/>
-      <c r="J215" t="inlineStr">
+      <c r="J215" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11152,7 +11084,7 @@
       </c>
       <c r="G216" s="26" t="n"/>
       <c r="H216" s="26" t="n"/>
-      <c r="J216" t="inlineStr">
+      <c r="J216" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11187,7 +11119,7 @@
       </c>
       <c r="G217" s="26" t="n"/>
       <c r="H217" s="26" t="n"/>
-      <c r="J217" t="inlineStr">
+      <c r="J217" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11222,7 +11154,7 @@
       </c>
       <c r="G218" s="26" t="n"/>
       <c r="H218" s="26" t="n"/>
-      <c r="J218" t="inlineStr">
+      <c r="J218" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11257,7 +11189,7 @@
       </c>
       <c r="G219" s="26" t="n"/>
       <c r="H219" s="26" t="n"/>
-      <c r="J219" t="inlineStr">
+      <c r="J219" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11292,7 +11224,7 @@
       </c>
       <c r="G220" s="26" t="n"/>
       <c r="H220" s="26" t="n"/>
-      <c r="J220" t="inlineStr">
+      <c r="J220" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11362,7 +11294,7 @@
       </c>
       <c r="G222" s="26" t="n"/>
       <c r="H222" s="26" t="n"/>
-      <c r="J222" t="inlineStr">
+      <c r="J222" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11397,7 +11329,7 @@
       </c>
       <c r="G223" s="26" t="n"/>
       <c r="H223" s="26" t="n"/>
-      <c r="J223" t="inlineStr">
+      <c r="J223" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11432,7 +11364,7 @@
       </c>
       <c r="G224" s="26" t="n"/>
       <c r="H224" s="26" t="n"/>
-      <c r="J224" t="inlineStr">
+      <c r="J224" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11467,7 +11399,7 @@
       </c>
       <c r="G225" s="26" t="n"/>
       <c r="H225" s="26" t="n"/>
-      <c r="J225" t="inlineStr">
+      <c r="J225" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11502,7 +11434,7 @@
       </c>
       <c r="G226" s="26" t="n"/>
       <c r="H226" s="26" t="n"/>
-      <c r="J226" t="inlineStr">
+      <c r="J226" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11537,7 +11469,7 @@
       </c>
       <c r="G227" s="26" t="n"/>
       <c r="H227" s="26" t="n"/>
-      <c r="J227" t="inlineStr">
+      <c r="J227" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11572,7 +11504,7 @@
       </c>
       <c r="G228" s="26" t="n"/>
       <c r="H228" s="26" t="n"/>
-      <c r="J228" t="inlineStr">
+      <c r="J228" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11607,7 +11539,7 @@
       </c>
       <c r="G229" s="26" t="n"/>
       <c r="H229" s="26" t="n"/>
-      <c r="J229" t="inlineStr">
+      <c r="J229" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11642,7 +11574,7 @@
       </c>
       <c r="G230" s="26" t="n"/>
       <c r="H230" s="26" t="n"/>
-      <c r="J230" t="inlineStr">
+      <c r="J230" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11677,7 +11609,7 @@
       </c>
       <c r="G231" s="26" t="n"/>
       <c r="H231" s="26" t="n"/>
-      <c r="J231" t="inlineStr">
+      <c r="J231" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11712,7 +11644,7 @@
       </c>
       <c r="G232" s="26" t="n"/>
       <c r="H232" s="26" t="n"/>
-      <c r="J232" t="inlineStr">
+      <c r="J232" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11747,7 +11679,7 @@
       </c>
       <c r="G233" s="26" t="n"/>
       <c r="H233" s="26" t="n"/>
-      <c r="J233" t="inlineStr">
+      <c r="J233" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11782,7 +11714,7 @@
       </c>
       <c r="G234" s="26" t="n"/>
       <c r="H234" s="26" t="n"/>
-      <c r="J234" t="inlineStr">
+      <c r="J234" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11817,7 +11749,7 @@
       </c>
       <c r="G235" s="26" t="n"/>
       <c r="H235" s="26" t="n"/>
-      <c r="J235" t="inlineStr">
+      <c r="J235" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -11852,7 +11784,7 @@
       </c>
       <c r="G236" s="26" t="n"/>
       <c r="H236" s="26" t="n"/>
-      <c r="J236" t="inlineStr">
+      <c r="J236" s="15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -12111,7 +12043,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>vitim</t>
+          <t>kretzer</t>
         </is>
       </c>
       <c r="C10" s="28" t="inlineStr">
@@ -12381,7 +12313,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>bernardom</t>
+          <t>marucco</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
@@ -12624,7 +12556,7 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>vitim</t>
+          <t>kretzer</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
@@ -12705,7 +12637,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>bernardoc</t>
+          <t>correa</t>
         </is>
       </c>
       <c r="C32" s="28" t="inlineStr">
@@ -12840,7 +12772,7 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>gordo</t>
+          <t>vitor</t>
         </is>
       </c>
       <c r="C37" s="28" t="inlineStr">
@@ -13029,7 +12961,7 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>bernardom</t>
+          <t>marucco</t>
         </is>
       </c>
       <c r="C44" s="28" t="inlineStr">
@@ -13272,7 +13204,7 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>bernardoc</t>
+          <t>correa</t>
         </is>
       </c>
       <c r="C53" s="28" t="inlineStr">
@@ -13677,7 +13609,7 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>gordo</t>
+          <t>vitor</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
@@ -15000,7 +14932,7 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>gordo</t>
+          <t>vitor</t>
         </is>
       </c>
       <c r="C117" s="28" t="inlineStr">

--- a/dados/COPA_REVOADA_planilha.xlsx
+++ b/dados/COPA_REVOADA_planilha.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="15" min="1" max="2"/>
@@ -1725,7 +1725,7 @@
       <c r="F7" s="25" t="n"/>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>Berna</t>
+          <t>Berna / Mito</t>
         </is>
       </c>
     </row>
@@ -2349,83 +2349,87 @@
     <row r="33" ht="15" customHeight="1" s="16">
       <c r="A33" s="25" t="inlineStr">
         <is>
-          <t>mito</t>
+          <t>nathan</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>Mito</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="C33" s="26" t="n"/>
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="26" t="n"/>
-      <c r="F33" s="25" t="n"/>
+      <c r="F33" s="25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>Mito</t>
+          <t>Nathan / nathan</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="16">
       <c r="A34" s="25" t="inlineStr">
         <is>
-          <t>nathan</t>
+          <t>pairobson</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>Nathan</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="n"/>
+          <t>Pai Robson</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
       <c r="D34" s="26" t="n"/>
       <c r="E34" s="26" t="n"/>
-      <c r="F34" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="F34" s="25" t="n"/>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>Nathan / nathan</t>
+          <t>Pai Robson</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="16">
       <c r="A35" s="25" t="inlineStr">
         <is>
-          <t>pairobson</t>
+          <t>phelps</t>
         </is>
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>Pai Robson</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="inlineStr">
-        <is>
-          <t>Mauro</t>
-        </is>
-      </c>
+          <t>Phelps</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="n"/>
       <c r="D35" s="26" t="n"/>
       <c r="E35" s="26" t="n"/>
-      <c r="F35" s="25" t="n"/>
+      <c r="F35" s="25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>Pai Robson</t>
+          <t>Felps / Phelps / phelps</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="16">
       <c r="A36" s="25" t="inlineStr">
         <is>
-          <t>phelps</t>
+          <t>pietro</t>
         </is>
       </c>
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>Phelps</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="C36" s="26" t="n"/>
@@ -2438,19 +2442,19 @@
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>Felps / Phelps / phelps</t>
+          <t>Pietro / pietro</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="16">
       <c r="A37" s="25" t="inlineStr">
         <is>
-          <t>pietro</t>
+          <t>probst</t>
         </is>
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Probst</t>
         </is>
       </c>
       <c r="C37" s="26" t="n"/>
@@ -2463,65 +2467,65 @@
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>Pietro / pietro</t>
+          <t>Probst / probst</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="16">
       <c r="A38" s="25" t="inlineStr">
         <is>
-          <t>probst</t>
+          <t>robson</t>
         </is>
       </c>
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>Probst</t>
+          <t>Robson</t>
         </is>
       </c>
       <c r="C38" s="26" t="n"/>
       <c r="D38" s="26" t="n"/>
       <c r="E38" s="26" t="n"/>
-      <c r="F38" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="F38" s="25" t="n"/>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>Probst / probst</t>
+          <t>Robson</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="16">
       <c r="A39" s="25" t="inlineStr">
         <is>
-          <t>robson</t>
+          <t>sograo</t>
         </is>
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>Robson</t>
+          <t>Sograo</t>
         </is>
       </c>
       <c r="C39" s="26" t="n"/>
       <c r="D39" s="26" t="n"/>
       <c r="E39" s="26" t="n"/>
-      <c r="F39" s="25" t="n"/>
+      <c r="F39" s="25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>Robson</t>
+          <t>sograo</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="16">
       <c r="A40" s="25" t="inlineStr">
         <is>
-          <t>sograo</t>
+          <t>vicente</t>
         </is>
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>Sograo</t>
+          <t>Vicente</t>
         </is>
       </c>
       <c r="C40" s="26" t="n"/>
@@ -2534,19 +2538,19 @@
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>sograo</t>
+          <t>vicente</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="16">
       <c r="A41" s="25" t="inlineStr">
         <is>
-          <t>vicente</t>
+          <t>vitao</t>
         </is>
       </c>
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>Vicente</t>
+          <t>Vitao</t>
         </is>
       </c>
       <c r="C41" s="26" t="n"/>
@@ -2559,19 +2563,19 @@
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>vicente</t>
+          <t>Vitao / vitao</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="16">
       <c r="A42" s="25" t="inlineStr">
         <is>
-          <t>vitao</t>
+          <t>vitor</t>
         </is>
       </c>
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>Vitao</t>
+          <t>Vitor</t>
         </is>
       </c>
       <c r="C42" s="26" t="n"/>
@@ -2584,19 +2588,19 @@
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>Vitao / vitao</t>
+          <t>gordo</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="16">
       <c r="A43" s="25" t="inlineStr">
         <is>
-          <t>vitor</t>
+          <t>zaga</t>
         </is>
       </c>
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>Vitor</t>
+          <t>Zaga</t>
         </is>
       </c>
       <c r="C43" s="26" t="n"/>
@@ -2609,35 +2613,11 @@
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>gordo</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="16">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>zaga</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="inlineStr">
-        <is>
-          <t>Zaga</t>
-        </is>
-      </c>
-      <c r="C44" s="26" t="n"/>
-      <c r="D44" s="26" t="n"/>
-      <c r="E44" s="26" t="n"/>
-      <c r="F44" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G44" s="25" t="inlineStr">
-        <is>
           <t>Zaga / zaga</t>
         </is>
       </c>
     </row>
+    <row r="44" ht="15" customHeight="1" s="16"/>
     <row r="45" ht="15" customHeight="1" s="16"/>
     <row r="46" ht="15" customHeight="1" s="16"/>
     <row r="47" ht="15" customHeight="1" s="16"/>
@@ -2770,7 +2750,11 @@
           <t>#E30613</t>
         </is>
       </c>
-      <c r="G5" s="26" t="n"/>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>pegueisuagatalogo.png</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="16">
       <c r="A6" s="25" t="inlineStr">
@@ -2832,7 +2816,11 @@
           <t>#E30613</t>
         </is>
       </c>
-      <c r="G7" s="26" t="n"/>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>pegueisuagatalogo.png</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="16">
       <c r="A8" s="25" t="inlineStr">
@@ -2987,7 +2975,11 @@
           <t>#141414</t>
         </is>
       </c>
-      <c r="G12" s="26" t="n"/>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>dboafclogo.png</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="16">
       <c r="A13" s="25" t="inlineStr">
@@ -3018,7 +3010,11 @@
           <t>#F2EFE5</t>
         </is>
       </c>
-      <c r="G13" s="26" t="n"/>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>criseumafclogo.png</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="16">
       <c r="A14" s="25" t="inlineStr">
@@ -3910,7 +3906,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>mito</t>
+          <t>berna</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -11028,7 +11024,7 @@
       </c>
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>leobittencourt</t>
         </is>
       </c>
       <c r="C215" s="25" t="inlineStr">
@@ -11962,7 +11958,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>mito</t>
+          <t>berna</t>
         </is>
       </c>
       <c r="C7" s="28" t="inlineStr">

--- a/dados/COPA_REVOADA_planilha.xlsx
+++ b/dados/COPA_REVOADA_planilha.xlsx
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>Arthur gk</t>
+          <t>Arthur</t>
         </is>
       </c>
       <c r="C5" s="26" t="n"/>
@@ -2254,7 +2254,11 @@
         </is>
       </c>
       <c r="C29" s="26" t="n"/>
-      <c r="D29" s="26" t="n"/>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>GOL</t>
+        </is>
+      </c>
       <c r="E29" s="26" t="n"/>
       <c r="F29" s="25" t="inlineStr">
         <is>
@@ -2300,7 +2304,7 @@
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>Merizi GK</t>
+          <t>Merizi</t>
         </is>
       </c>
       <c r="C31" s="26" t="n"/>
@@ -2379,7 +2383,7 @@
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>Pai Robson</t>
+          <t>Mauro</t>
         </is>
       </c>
       <c r="C34" s="26" t="inlineStr">

--- a/dados/COPA_REVOADA_planilha.xlsx
+++ b/dados/COPA_REVOADA_planilha.xlsx
@@ -2653,7 +2653,7 @@
     <row r="1" ht="15" customHeight="1" s="16">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>As cores são chute meu a partir do nome. Troque à vontade.</t>
+          <t>As cores desenham o escudo e as faixas das artes. Evite verde: o Estúdio exporta WebM em fundo verde e o Chroma Key comeria a peça junto.</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t>#12A150</t>
+          <t>#F2B01E</t>
         </is>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>#F2EFE5</t>
+          <t>#17181A</t>
         </is>
       </c>
       <c r="G16" s="26" t="n"/>

--- a/dados/COPA_REVOADA_planilha.xlsx
+++ b/dados/COPA_REVOADA_planilha.xlsx
@@ -18,6 +18,8 @@
     <sheet name="PENDENCIAS" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="LISTAS" sheetId="10" state="hidden" r:id="rId10"/>
     <sheet name="CONFERE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="LANCES 2026-04" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="LANCES 2026-08" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -176,7 +178,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -274,6 +276,7 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1568,6 +1571,180 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="16" min="1" max="1"/>
+    <col width="8" customWidth="1" style="16" min="2" max="2"/>
+    <col width="14" customWidth="1" style="16" min="3" max="3"/>
+    <col width="18" customWidth="1" style="16" min="4" max="4"/>
+    <col width="8" customWidth="1" style="16" min="5" max="5"/>
+    <col width="16" customWidth="1" style="16" min="6" max="6"/>
+    <col width="20" customWidth="1" style="16" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Lances marcados deste jogo. O app grava e lê daqui. A chave abaixo é o que libera a edição no app — trate como senha do grupo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>chave_de_acesso</t>
+        </is>
+      </c>
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>RVD-GLM7-4P84</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>dentro26 x ferroviagra26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>jogador</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>xg</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>por</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="16" min="1" max="1"/>
+    <col width="8" customWidth="1" style="16" min="2" max="2"/>
+    <col width="14" customWidth="1" style="16" min="3" max="3"/>
+    <col width="18" customWidth="1" style="16" min="4" max="4"/>
+    <col width="8" customWidth="1" style="16" min="5" max="5"/>
+    <col width="16" customWidth="1" style="16" min="6" max="6"/>
+    <col width="20" customWidth="1" style="16" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Lances marcados deste jogo. O app grava e lê daqui. A chave abaixo é o que libera a edição no app — trate como senha do grupo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>chave_de_acesso</t>
+        </is>
+      </c>
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>RVD-G3JJ-BB2P</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>dentro26 x ferroviagra26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>jogador</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>xg</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>por</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/dados/COPA_REVOADA_planilha.xlsx
+++ b/dados/COPA_REVOADA_planilha.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -95,6 +95,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="9">
@@ -178,7 +182,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -277,6 +281,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1602,9 +1608,14 @@
           <t>chave_de_acesso</t>
         </is>
       </c>
-      <c r="B2" s="37" t="inlineStr">
-        <is>
-          <t>RVD-GLM7-4P84</t>
+      <c r="B2" s="38" t="inlineStr">
+        <is>
+          <t>TROQUE-ESTA-CHAVE</t>
+        </is>
+      </c>
+      <c r="C2" s="39" t="inlineStr">
+        <is>
+          <t>&lt;- digite a sua aqui, depois de subir pro Drive</t>
         </is>
       </c>
       <c r="D2" s="28" t="inlineStr">
@@ -1689,9 +1700,14 @@
           <t>chave_de_acesso</t>
         </is>
       </c>
-      <c r="B2" s="37" t="inlineStr">
-        <is>
-          <t>RVD-G3JJ-BB2P</t>
+      <c r="B2" s="38" t="inlineStr">
+        <is>
+          <t>TROQUE-ESTA-CHAVE</t>
+        </is>
+      </c>
+      <c r="C2" s="39" t="inlineStr">
+        <is>
+          <t>&lt;- digite a sua aqui, depois de subir pro Drive</t>
         </is>
       </c>
       <c r="D2" s="28" t="inlineStr">

--- a/dados/COPA_REVOADA_planilha.xlsx
+++ b/dados/COPA_REVOADA_planilha.xlsx
@@ -8,18 +8,19 @@
   </bookViews>
   <sheets>
     <sheet name="LEIA-ME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="JOGADORES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TIMES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="JOGOS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ESCALACOES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DESEMPENHO" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TROFEUS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="CLIPES" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="PENDENCIAS" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="LISTAS" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet name="CONFERE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="LANCES 2026-04" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="LANCES 2026-08" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="CONFIG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="JOGADORES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TIMES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="JOGOS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ESCALACOES" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DESEMPENHO" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TROFEUS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="CLIPES" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="PENDENCIAS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="LISTAS" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet name="CONFERE" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="LANCES 2026-04" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="LANCES 2026-08" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -744,488 +745,474 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="6" customWidth="1" style="15" min="1" max="1"/>
+    <col width="11" customWidth="1" style="15" min="2" max="2"/>
+    <col width="96" customWidth="1" style="15" min="3" max="3"/>
+    <col width="16" customWidth="1" style="15" min="4" max="4"/>
+    <col width="15" customWidth="1" style="15" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="16">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>andre</t>
-        </is>
-      </c>
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>chelsea20</t>
-        </is>
-      </c>
-      <c r="C1" s="15" t="inlineStr">
-        <is>
-          <t>2020-12</t>
-        </is>
-      </c>
-      <c r="D1" s="15" t="inlineStr">
-        <is>
-          <t>campeao</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="16">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>arthur</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>psg20</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>2021-07</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>artilheiro</t>
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Prioridade 1 é o que mais atrapalha o site.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="16">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>bala</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>chelsea21</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>2021-12</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>garcom</t>
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>prio</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>o que resolver</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>quem</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>resolvido em</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="16">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>berna</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>psg21</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>2022-04</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>craque</t>
-        </is>
-      </c>
+      <c r="A4" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>gols</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>2020-12: a planilha antiga não guardou gols por jogador nesse jogo</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="26" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="16">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>bernardoc</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>liverpool22</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>2022-08</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>paredao</t>
-        </is>
-      </c>
+      <c r="A5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>gols</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>2021-07: a planilha antiga não guardou gols por jogador nesse jogo</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="16">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>bernardom</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>borussia22</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>2022-10</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>piroquinha</t>
-        </is>
-      </c>
+      <c r="A6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>gols</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
+        <is>
+          <t>2021-12: a planilha antiga não guardou gols por jogador nesse jogo</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="26" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="16">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>borba</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>boca23</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>2023-06</t>
-        </is>
-      </c>
+      <c r="A7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>gols</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>2024-12: gols lançados somam 7, placar é 5+3=8</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="26" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="16">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>bruno</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>city23</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>2023-10</t>
-        </is>
-      </c>
+      <c r="A8" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>gols</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>2026-08: gols lançados somam 3, placar é 1+1=2</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="26" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="16">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>correa</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>branco24</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
+      <c r="A9" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>lados</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>2022-08: placar empatado, não dá pra deduzir qual lado é liverpool22 e qual é borussia22 — confirme</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="26" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="16">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>danilim</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>preto24</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
+      <c r="A10" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>lados</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="inlineStr">
+        <is>
+          <t>2023-06: placar empatado, não dá pra deduzir qual lado é boca23 e qual é city23 — confirme</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="16">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>davi</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>milanbe25</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
+      <c r="A11" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>'Berna' aparece nas escalações mas não está no RANKING Atual</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="16">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>dereck</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>jumentus25</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
+      <c r="A12" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>'Bernardo C' aparece nas escalações mas não está no RANKING Atual</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="16">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>derek</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>dentro26</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
+      <c r="A13" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>'Bernardo M' aparece nas escalações mas não está no RANKING Atual</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="16">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>dereka</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>ferroviagra26</t>
-        </is>
-      </c>
+      <c r="A14" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>'Dereck' aparece nas escalações mas não está no RANKING Atual</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="n"/>
+      <c r="E14" s="26" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="16">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>enzo</t>
-        </is>
-      </c>
+      <c r="A15" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>'Derek' aparece nas escalações mas não está no RANKING Atual</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="n"/>
+      <c r="E15" s="26" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>fanta</t>
-        </is>
-      </c>
+      <c r="A16" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>'Dereka' aparece nas escalações mas não está no RANKING Atual</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="26" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="16">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>garopaba</t>
-        </is>
-      </c>
+      <c r="A17" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>'Gordo' aparece nas escalações mas não está no RANKING Atual</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="26" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="16">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>glauber</t>
-        </is>
-      </c>
+      <c r="A18" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>'Mito' aparece nas escalações mas não está no RANKING Atual</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="16">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>gordo</t>
-        </is>
-      </c>
+      <c r="A19" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="inlineStr">
+        <is>
+          <t>'Pai Robson' aparece nas escalações mas não está no RANKING Atual</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="16">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>hanon</t>
-        </is>
-      </c>
+      <c r="A20" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>'Robson' aparece nas escalações mas não está no RANKING Atual</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="n"/>
+      <c r="E20" s="26" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="16">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>henrique</t>
-        </is>
-      </c>
+      <c r="A21" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>'Vitim' aparece nas escalações mas não está no RANKING Atual</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="26" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="16">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>joao</t>
-        </is>
-      </c>
+      <c r="A22" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>'garopaba' aparece escrito como: Garopa, Garopaba, garopa, garopaba — confirme se é a mesma pessoa</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="26" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="16">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>kretzer</t>
-        </is>
-      </c>
+      <c r="A23" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>'mito' só aparece uma vez, sem apelido completo</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="n"/>
+      <c r="E23" s="26" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="16">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>leo</t>
-        </is>
-      </c>
+      <c r="A24" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="inlineStr">
+        <is>
+          <t>'phelps' aparece escrito como: Felps, Phelps, phelps — confirme se é a mesma pessoa</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="n"/>
+      <c r="E24" s="26" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="16">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>leobittencourt</t>
-        </is>
-      </c>
+      <c r="A25" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>são a mesma pessoa? bernardoc, bernardom, berna — se sim, me diga o id que fica</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="26" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="16">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>leogodinho</t>
-        </is>
-      </c>
+      <c r="A26" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="inlineStr">
+        <is>
+          <t>são a mesma pessoa? derek, dereck, dereka — se sim, me diga o id que fica</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="26" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="16">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>letti</t>
-        </is>
-      </c>
+      <c r="A27" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>são a mesma pessoa? robson, pairobson — se sim, me diga o id que fica</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="n"/>
+      <c r="E27" s="26" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="16">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>luigi</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="16">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>marucco</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="16">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>matheus</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="16">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>merizi</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="16">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>miniderek</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="16">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>mito</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="16">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>nathan</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="16">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>pairobson</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="16">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>phelps</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="16">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>pietro</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="16">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>probst</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="16">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>robson</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="16">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>sograo</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="16">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>vicente</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="16">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>vitao</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="16">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>vitim</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="16">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>vitor</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="16">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>zaga</t>
-        </is>
-      </c>
+      <c r="A28" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>nomes</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="inlineStr">
+        <is>
+          <t>são a mesma pessoa? vitim, vitor — se sim, me diga o id que fica</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="n"/>
+      <c r="E28" s="26" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1235,6 +1222,502 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1" s="16">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>andre</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>chelsea20</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>campeao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="16">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>arthur</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>psg20</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>artilheiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="16">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>bala</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>chelsea21</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>garcom</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="16">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>berna</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>psg21</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>craque</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="16">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>bernardoc</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>liverpool22</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>paredao</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="16">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>bernardom</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>borussia22</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>piroquinha</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="16">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>borba</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>boca23</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="16">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>bruno</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>city23</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="16">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>correa</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>branco24</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="16">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>danilim</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>preto24</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="16">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>davi</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>milanbe25</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="16">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>dereck</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>jumentus25</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="16">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>derek</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>dentro26</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="16">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>dereka</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>ferroviagra26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="16">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>enzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>fanta</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="16">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>garopaba</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="16">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>glauber</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="16">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>gordo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="16">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>hanon</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="16">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>henrique</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="16">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>joao</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="16">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>kretzer</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="16">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="16">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>leobittencourt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="16">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>leogodinho</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="16">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>letti</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="16">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>luigi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="16">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>marucco</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="16">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>matheus</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="16">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>merizi</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="16">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>miniderek</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="16">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>mito</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="16">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>nathan</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="16">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>pairobson</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="16">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>phelps</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="16">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>pietro</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="16">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>probst</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="16">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>robson</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="16">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>sograo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="16">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>vicente</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="16">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>vitao</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="16">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>vitim</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="16">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>vitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="16">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>zaga</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1574,98 +2057,6 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" style="16" min="1" max="1"/>
-    <col width="8" customWidth="1" style="16" min="2" max="2"/>
-    <col width="14" customWidth="1" style="16" min="3" max="3"/>
-    <col width="18" customWidth="1" style="16" min="4" max="4"/>
-    <col width="8" customWidth="1" style="16" min="5" max="5"/>
-    <col width="16" customWidth="1" style="16" min="6" max="6"/>
-    <col width="20" customWidth="1" style="16" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>Lances marcados deste jogo. O app grava e lê daqui. A chave abaixo é o que libera a edição no app — trate como senha do grupo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>chave_de_acesso</t>
-        </is>
-      </c>
-      <c r="B2" s="38" t="inlineStr">
-        <is>
-          <t>TROQUE-ESTA-CHAVE</t>
-        </is>
-      </c>
-      <c r="C2" s="39" t="inlineStr">
-        <is>
-          <t>&lt;- digite a sua aqui, depois de subir pro Drive</t>
-        </is>
-      </c>
-      <c r="D2" s="28" t="inlineStr">
-        <is>
-          <t>dentro26 x ferroviagra26</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="B4" s="30" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C4" s="30" t="inlineStr">
-        <is>
-          <t>tipo</t>
-        </is>
-      </c>
-      <c r="D4" s="30" t="inlineStr">
-        <is>
-          <t>jogador</t>
-        </is>
-      </c>
-      <c r="E4" s="30" t="inlineStr">
-        <is>
-          <t>xg</t>
-        </is>
-      </c>
-      <c r="F4" s="30" t="inlineStr">
-        <is>
-          <t>por</t>
-        </is>
-      </c>
-      <c r="G4" s="30" t="inlineStr">
-        <is>
-          <t>em</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1761,7 +2152,145 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="16" min="1" max="1"/>
+    <col width="8" customWidth="1" style="16" min="2" max="2"/>
+    <col width="14" customWidth="1" style="16" min="3" max="3"/>
+    <col width="18" customWidth="1" style="16" min="4" max="4"/>
+    <col width="8" customWidth="1" style="16" min="5" max="5"/>
+    <col width="16" customWidth="1" style="16" min="6" max="6"/>
+    <col width="20" customWidth="1" style="16" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Lances marcados deste jogo. O app grava e lê daqui. A chave abaixo é o que libera a edição no app — trate como senha do grupo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>chave_de_acesso</t>
+        </is>
+      </c>
+      <c r="B2" s="38" t="inlineStr">
+        <is>
+          <t>TROQUE-ESTA-CHAVE</t>
+        </is>
+      </c>
+      <c r="C2" s="39" t="inlineStr">
+        <is>
+          <t>&lt;- digite a sua aqui, depois de subir pro Drive</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>dentro26 x ferroviagra26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>jogador</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>xg</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>por</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="16" min="1" max="1"/>
+    <col width="26" customWidth="1" style="16" min="2" max="2"/>
+    <col width="52" customWidth="1" style="16" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Chave mestra: é ela que autoriza o app a criar a aba de um jogo novo. Cada aba de jogo tem a sua própria chave na célula B2 dela.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>chave_mestra</t>
+        </is>
+      </c>
+      <c r="B2" s="38" t="inlineStr">
+        <is>
+          <t>TROQUE-ESTA-CHAVE</t>
+        </is>
+      </c>
+      <c r="C2" s="39" t="inlineStr">
+        <is>
+          <t>&lt;- digite a sua aqui; nunca comitar no repositório</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2826,7 +3355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3344,7 +3873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3955,7 +4484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12004,7 +12533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16259,7 +16788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16528,7 +17057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16637,486 +17166,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="6" customWidth="1" style="15" min="1" max="1"/>
-    <col width="11" customWidth="1" style="15" min="2" max="2"/>
-    <col width="96" customWidth="1" style="15" min="3" max="3"/>
-    <col width="16" customWidth="1" style="15" min="4" max="4"/>
-    <col width="15" customWidth="1" style="15" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" s="16">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>Prioridade 1 é o que mais atrapalha o site.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="16">
-      <c r="A3" s="24" t="inlineStr">
-        <is>
-          <t>prio</t>
-        </is>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>tipo</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>o que resolver</t>
-        </is>
-      </c>
-      <c r="D3" s="24" t="inlineStr">
-        <is>
-          <t>quem</t>
-        </is>
-      </c>
-      <c r="E3" s="24" t="inlineStr">
-        <is>
-          <t>resolvido em</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="16">
-      <c r="A4" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="34" t="inlineStr">
-        <is>
-          <t>gols</t>
-        </is>
-      </c>
-      <c r="C4" s="34" t="inlineStr">
-        <is>
-          <t>2020-12: a planilha antiga não guardou gols por jogador nesse jogo</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="n"/>
-      <c r="E4" s="26" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="16">
-      <c r="A5" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="34" t="inlineStr">
-        <is>
-          <t>gols</t>
-        </is>
-      </c>
-      <c r="C5" s="34" t="inlineStr">
-        <is>
-          <t>2021-07: a planilha antiga não guardou gols por jogador nesse jogo</t>
-        </is>
-      </c>
-      <c r="D5" s="26" t="n"/>
-      <c r="E5" s="26" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="16">
-      <c r="A6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="34" t="inlineStr">
-        <is>
-          <t>gols</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="inlineStr">
-        <is>
-          <t>2021-12: a planilha antiga não guardou gols por jogador nesse jogo</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="n"/>
-      <c r="E6" s="26" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="16">
-      <c r="A7" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>gols</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="inlineStr">
-        <is>
-          <t>2024-12: gols lançados somam 7, placar é 5+3=8</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="n"/>
-      <c r="E7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="16">
-      <c r="A8" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="34" t="inlineStr">
-        <is>
-          <t>gols</t>
-        </is>
-      </c>
-      <c r="C8" s="34" t="inlineStr">
-        <is>
-          <t>2026-08: gols lançados somam 3, placar é 1+1=2</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="n"/>
-      <c r="E8" s="26" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="16">
-      <c r="A9" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>lados</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t>2022-08: placar empatado, não dá pra deduzir qual lado é liverpool22 e qual é borussia22 — confirme</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="n"/>
-      <c r="E9" s="26" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="16">
-      <c r="A10" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>lados</t>
-        </is>
-      </c>
-      <c r="C10" s="34" t="inlineStr">
-        <is>
-          <t>2023-06: placar empatado, não dá pra deduzir qual lado é boca23 e qual é city23 — confirme</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="16">
-      <c r="A11" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t>'Berna' aparece nas escalações mas não está no RANKING Atual</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="16">
-      <c r="A12" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C12" s="34" t="inlineStr">
-        <is>
-          <t>'Bernardo C' aparece nas escalações mas não está no RANKING Atual</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="16">
-      <c r="A13" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="inlineStr">
-        <is>
-          <t>'Bernardo M' aparece nas escalações mas não está no RANKING Atual</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="16">
-      <c r="A14" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B14" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t>'Dereck' aparece nas escalações mas não está no RANKING Atual</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="16">
-      <c r="A15" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t>'Derek' aparece nas escalações mas não está no RANKING Atual</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="26" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="16">
-      <c r="A16" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="inlineStr">
-        <is>
-          <t>'Dereka' aparece nas escalações mas não está no RANKING Atual</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="26" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="16">
-      <c r="A17" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C17" s="34" t="inlineStr">
-        <is>
-          <t>'Gordo' aparece nas escalações mas não está no RANKING Atual</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="n"/>
-      <c r="E17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="16">
-      <c r="A18" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="inlineStr">
-        <is>
-          <t>'Mito' aparece nas escalações mas não está no RANKING Atual</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="n"/>
-      <c r="E18" s="26" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="16">
-      <c r="A19" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="inlineStr">
-        <is>
-          <t>'Pai Robson' aparece nas escalações mas não está no RANKING Atual</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="n"/>
-      <c r="E19" s="26" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="16">
-      <c r="A20" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B20" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C20" s="34" t="inlineStr">
-        <is>
-          <t>'Robson' aparece nas escalações mas não está no RANKING Atual</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="n"/>
-      <c r="E20" s="26" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="16">
-      <c r="A21" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C21" s="34" t="inlineStr">
-        <is>
-          <t>'Vitim' aparece nas escalações mas não está no RANKING Atual</t>
-        </is>
-      </c>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="26" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="16">
-      <c r="A22" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C22" s="34" t="inlineStr">
-        <is>
-          <t>'garopaba' aparece escrito como: Garopa, Garopaba, garopa, garopaba — confirme se é a mesma pessoa</t>
-        </is>
-      </c>
-      <c r="D22" s="26" t="n"/>
-      <c r="E22" s="26" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="16">
-      <c r="A23" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C23" s="34" t="inlineStr">
-        <is>
-          <t>'mito' só aparece uma vez, sem apelido completo</t>
-        </is>
-      </c>
-      <c r="D23" s="26" t="n"/>
-      <c r="E23" s="26" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="16">
-      <c r="A24" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C24" s="34" t="inlineStr">
-        <is>
-          <t>'phelps' aparece escrito como: Felps, Phelps, phelps — confirme se é a mesma pessoa</t>
-        </is>
-      </c>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="26" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="16">
-      <c r="A25" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C25" s="34" t="inlineStr">
-        <is>
-          <t>são a mesma pessoa? bernardoc, bernardom, berna — se sim, me diga o id que fica</t>
-        </is>
-      </c>
-      <c r="D25" s="26" t="n"/>
-      <c r="E25" s="26" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="16">
-      <c r="A26" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>são a mesma pessoa? derek, dereck, dereka — se sim, me diga o id que fica</t>
-        </is>
-      </c>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="26" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="16">
-      <c r="A27" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B27" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>são a mesma pessoa? robson, pairobson — se sim, me diga o id que fica</t>
-        </is>
-      </c>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="16">
-      <c r="A28" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B28" s="34" t="inlineStr">
-        <is>
-          <t>nomes</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="inlineStr">
-        <is>
-          <t>são a mesma pessoa? vitim, vitor — se sim, me diga o id que fica</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="26" t="n"/>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
 </file>
--- a/dados/COPA_REVOADA_planilha.xlsx
+++ b/dados/COPA_REVOADA_planilha.xlsx
@@ -12,15 +12,16 @@
     <sheet name="JOGADORES" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="TIMES" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="JOGOS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ESCALACOES" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DESEMPENHO" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TROFEUS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CLIPES" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="PENDENCIAS" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LISTAS" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet name="CONFERE" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="LANCES 2026-04" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="LANCES 2026-08" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="VIDEOS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ESCALACOES" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DESEMPENHO" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TROFEUS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="CLIPES" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="PENDENCIAS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="LISTAS" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet name="CONFERE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="LANCES 2026-04" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="LANCES 2026-08" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -745,6 +746,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="17" customWidth="1" style="15" min="1" max="1"/>
+    <col width="32" customWidth="1" style="15" min="2" max="2"/>
+    <col width="17" customWidth="1" style="15" min="3" max="3"/>
+    <col width="11" customWidth="1" style="15" min="4" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1" s="16">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Linhas EXEMPLO são ignoradas. Não corte vídeo: o site recorta pelo início e fim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="16">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>jogador_id</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>video_youtube</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>inicio_seg</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>fim_seg</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>temporada</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="16">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>EXEMPLO</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>Hat-trick na final</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n">
+        <v>412</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>438</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="16">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>EXEMPLO</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Golaço de fora da área</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n">
+        <v>95</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>118</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A4:A900" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+      <formula1>LISTAS!$A$1:$A$45</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
@@ -1221,7 +1333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1717,7 +1829,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2060,7 +2172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2152,7 +2264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4486,6 +4598,181 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="16" min="1" max="1"/>
+    <col width="26" customWidth="1" style="16" min="2" max="2"/>
+    <col width="34" customWidth="1" style="16" min="3" max="3"/>
+    <col width="12" customWidth="1" style="16" min="4" max="4"/>
+    <col width="40" customWidth="1" style="16" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Um vídeo por jogo. Cole só o ID do YouTube (o que vem depois de v= na URL). É daqui que a tela de Vídeos monta os cards. Os melhores momentos continuam na aba CLIPES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>jogo_id</t>
+        </is>
+      </c>
+      <c r="B3" s="30" t="inlineStr">
+        <is>
+          <t>video_youtube</t>
+        </is>
+      </c>
+      <c r="C3" s="30" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>duracao</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>observacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="n"/>
+      <c r="C4" s="31" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="31" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="31" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="31" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="31" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="31" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="31" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="31" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="31" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -12533,7 +12820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16788,7 +17075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17055,115 +17342,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="17" customWidth="1" style="15" min="1" max="1"/>
-    <col width="32" customWidth="1" style="15" min="2" max="2"/>
-    <col width="17" customWidth="1" style="15" min="3" max="3"/>
-    <col width="11" customWidth="1" style="15" min="4" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" s="16">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>Linhas EXEMPLO são ignoradas. Não corte vídeo: o site recorta pelo início e fim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="16">
-      <c r="A3" s="24" t="inlineStr">
-        <is>
-          <t>jogador_id</t>
-        </is>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>titulo</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>video_youtube</t>
-        </is>
-      </c>
-      <c r="D3" s="24" t="inlineStr">
-        <is>
-          <t>inicio_seg</t>
-        </is>
-      </c>
-      <c r="E3" s="24" t="inlineStr">
-        <is>
-          <t>fim_seg</t>
-        </is>
-      </c>
-      <c r="F3" s="24" t="inlineStr">
-        <is>
-          <t>temporada</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="16">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>EXEMPLO</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>Hat-trick na final</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="n"/>
-      <c r="D4" s="26" t="n">
-        <v>412</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>438</v>
-      </c>
-      <c r="F4" s="26" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="16">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>EXEMPLO</t>
-        </is>
-      </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>Golaço de fora da área</t>
-        </is>
-      </c>
-      <c r="C5" s="26" t="n"/>
-      <c r="D5" s="26" t="n">
-        <v>95</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>118</v>
-      </c>
-      <c r="F5" s="26" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A4:A900" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>LISTAS!$A$1:$A$45</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
 </file>
--- a/dados/COPA_REVOADA_planilha.xlsx
+++ b/dados/COPA_REVOADA_planilha.xlsx
@@ -3720,7 +3720,11 @@
           <t>#141414</t>
         </is>
       </c>
-      <c r="G9" s="26" t="n"/>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>borussetalogo.png</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="16">
       <c r="A10" s="25" t="inlineStr">
@@ -3751,7 +3755,11 @@
           <t>#F2C14E</t>
         </is>
       </c>
-      <c r="G10" s="26" t="n"/>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>bocalogo.png</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="16">
       <c r="A11" s="25" t="inlineStr">
@@ -3782,7 +3790,11 @@
           <t>#0B2A4A</t>
         </is>
       </c>
-      <c r="G11" s="26" t="n"/>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>mancitylogo.png</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="16">
       <c r="A12" s="25" t="inlineStr">
@@ -3792,7 +3804,7 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>DBOAFC</t>
         </is>
       </c>
       <c r="C12" s="25" t="n">
@@ -3800,7 +3812,7 @@
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>DBO</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
@@ -3827,7 +3839,7 @@
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>CRISEUMA</t>
         </is>
       </c>
       <c r="C13" s="25" t="n">
@@ -3835,7 +3847,7 @@
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>PRE</t>
+          <t>CRI</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
@@ -4647,7 +4659,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>2020-12</t>
         </is>
@@ -4656,7 +4668,7 @@
       <c r="C4" s="31" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>2021-07</t>
         </is>
@@ -4665,7 +4677,7 @@
       <c r="C5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>2021-12</t>
         </is>
@@ -4674,7 +4686,7 @@
       <c r="C6" s="31" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>2022-04</t>
         </is>
@@ -4683,7 +4695,7 @@
       <c r="C7" s="31" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>2022-08</t>
         </is>
@@ -4692,7 +4704,7 @@
       <c r="C8" s="31" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>2022-10</t>
         </is>
@@ -4701,7 +4713,7 @@
       <c r="C9" s="31" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>2023-06</t>
         </is>
@@ -4710,7 +4722,7 @@
       <c r="C10" s="31" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>2023-10</t>
         </is>
@@ -4719,7 +4731,7 @@
       <c r="C11" s="31" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
@@ -4728,7 +4740,7 @@
       <c r="C12" s="31" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
@@ -4737,7 +4749,7 @@
       <c r="C13" s="31" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -4746,7 +4758,7 @@
       <c r="C14" s="31" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -4755,7 +4767,7 @@
       <c r="C15" s="31" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
